--- a/Dev_GNC/TableData/PawnGrowthDataTable.xlsx
+++ b/Dev_GNC/TableData/PawnGrowthDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACA1E35-5749-4DE7-BD79-712757CB68AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E87CE7-590F-441F-BC78-160DC8788F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4E2CE612-1B7B-42D4-B304-89C013EEA25A}"/>
+    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{4E2CE612-1B7B-42D4-B304-89C013EEA25A}"/>
   </bookViews>
   <sheets>
     <sheet name="PawnGrowthData" sheetId="1" r:id="rId1"/>
@@ -88,37 +88,6 @@
     <t>pawn_growth_scount_10</t>
   </si>
   <si>
-    <t>pawn_growth_assult_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pawn_growth_assult_2</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_3</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_4</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_5</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_6</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_7</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_8</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_9</t>
-  </si>
-  <si>
-    <t>pawn_growth_assult_10</t>
-  </si>
-  <si>
     <t>pawn_growth_heavy_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -184,9 +153,6 @@
     <t>SCOUT</t>
   </si>
   <si>
-    <t>ASSULT</t>
-  </si>
-  <si>
     <t>HEAVY</t>
   </si>
   <si>
@@ -229,22 +195,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>card_assult_skill1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>card_assult_skill2</t>
-  </si>
-  <si>
-    <t>card_assult_skill3</t>
-  </si>
-  <si>
-    <t>card_assult_skill4</t>
-  </si>
-  <si>
-    <t>card_assult_skill5</t>
-  </si>
-  <si>
     <t>card_heavy_skill1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -278,6 +228,61 @@
   </si>
   <si>
     <t>requireExp</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pawn_growth_assault_2</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_3</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_4</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_5</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_6</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_7</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_8</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_9</t>
+  </si>
+  <si>
+    <t>pawn_growth_assault_10</t>
+  </si>
+  <si>
+    <t>ASSAULT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -724,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>4</v>
@@ -745,10 +750,10 @@
         <v>5</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -759,7 +764,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -768,16 +773,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -788,7 +793,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -797,7 +802,7 @@
         <v>200</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -811,7 +816,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -820,7 +825,7 @@
         <v>300</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -834,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -843,13 +848,13 @@
         <v>400</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -860,7 +865,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -869,13 +874,13 @@
         <v>500</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -889,7 +894,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -898,7 +903,7 @@
         <v>600</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -912,7 +917,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
@@ -921,13 +926,13 @@
         <v>700</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -938,7 +943,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
@@ -947,7 +952,7 @@
         <v>800</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -961,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
@@ -970,7 +975,7 @@
         <v>900</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -984,7 +989,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -993,19 +998,19 @@
         <v>1000</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1013,10 +1018,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -1025,16 +1030,16 @@
         <v>100</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1042,10 +1047,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -1054,7 +1059,7 @@
         <v>200</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1065,10 +1070,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -1077,7 +1082,7 @@
         <v>300</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1088,10 +1093,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1">
         <v>4</v>
@@ -1100,13 +1105,13 @@
         <v>400</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1114,10 +1119,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1">
         <v>5</v>
@@ -1126,7 +1131,7 @@
         <v>500</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G16" s="1">
         <v>1</v>
@@ -1137,10 +1142,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1">
         <v>6</v>
@@ -1149,13 +1154,13 @@
         <v>600</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G17" s="1">
         <v>2</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -1166,10 +1171,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1">
         <v>7</v>
@@ -1178,19 +1183,19 @@
         <v>700</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G18" s="1">
         <v>2</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1198,10 +1203,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1">
         <v>8</v>
@@ -1210,13 +1215,13 @@
         <v>800</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1">
         <v>2</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -1227,10 +1232,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D20" s="1">
         <v>9</v>
@@ -1239,13 +1244,13 @@
         <v>900</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G20" s="1">
         <v>2</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1256,10 +1261,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1">
         <v>10</v>
@@ -1268,19 +1273,19 @@
         <v>1000</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G21" s="1">
         <v>2</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -1288,10 +1293,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -1300,22 +1305,22 @@
         <v>100</v>
       </c>
       <c r="F22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -1323,10 +1328,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
@@ -1335,13 +1340,13 @@
         <v>200</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1352,10 +1357,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
@@ -1364,13 +1369,13 @@
         <v>300</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1381,10 +1386,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D25" s="1">
         <v>4</v>
@@ -1393,19 +1398,19 @@
         <v>400</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -1413,10 +1418,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D26" s="1">
         <v>5</v>
@@ -1425,13 +1430,13 @@
         <v>500</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -1442,10 +1447,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D27" s="1">
         <v>6</v>
@@ -1454,13 +1459,13 @@
         <v>600</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -1471,10 +1476,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D28" s="1">
         <v>7</v>
@@ -1483,19 +1488,19 @@
         <v>700</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -1503,10 +1508,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1">
         <v>8</v>
@@ -1515,13 +1520,13 @@
         <v>800</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -1532,10 +1537,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D30" s="1">
         <v>9</v>
@@ -1544,13 +1549,13 @@
         <v>900</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -1561,10 +1566,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D31" s="1">
         <v>10</v>
@@ -1573,19 +1578,19 @@
         <v>1000</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -1593,10 +1598,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -1605,16 +1610,16 @@
         <v>100</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1622,10 +1627,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -1634,7 +1639,7 @@
         <v>200</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -1645,10 +1650,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -1657,7 +1662,7 @@
         <v>300</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -1668,10 +1673,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D35" s="1">
         <v>4</v>
@@ -1680,13 +1685,13 @@
         <v>400</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1694,10 +1699,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D36" s="1">
         <v>5</v>
@@ -1706,13 +1711,13 @@
         <v>500</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -1723,10 +1728,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D37" s="1">
         <v>6</v>
@@ -1735,7 +1740,7 @@
         <v>600</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
@@ -1746,10 +1751,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D38" s="1">
         <v>7</v>
@@ -1758,13 +1763,13 @@
         <v>700</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -1772,10 +1777,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D39" s="1">
         <v>8</v>
@@ -1784,7 +1789,7 @@
         <v>800</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -1795,10 +1800,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D40" s="1">
         <v>9</v>
@@ -1807,7 +1812,7 @@
         <v>900</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
@@ -1818,10 +1823,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D41" s="1">
         <v>10</v>
@@ -1830,19 +1835,19 @@
         <v>1000</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G41" s="1">
         <v>2</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I41">
         <v>1</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
